--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 16,46</t>
+          <t>2,33; 16,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 8,17</t>
+          <t>-4,19; 7,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 10,01</t>
+          <t>-4,28; 9,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 11,05</t>
+          <t>-2,89; 10,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,76</t>
+          <t>-7,45; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 6,66</t>
+          <t>-7,28; 6,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,41</t>
+          <t>2,09; 11,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,71</t>
+          <t>-3,96; 5,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,53</t>
+          <t>-4,4; 5,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 630,02</t>
+          <t>16,01; 562,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 277,94</t>
+          <t>-47,87; 265,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 336,66</t>
+          <t>-50,69; 304,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 223,87</t>
+          <t>-25,35; 249,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 129,65</t>
+          <t>-64,15; 126,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 155,77</t>
+          <t>-71,34; 148,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 236,13</t>
+          <t>21,02; 267,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 103,68</t>
+          <t>-43,61; 125,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 121,57</t>
+          <t>-49,09; 120,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,33</t>
+          <t>-1,15; 7,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,71</t>
+          <t>0,07; 10,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 5,03</t>
+          <t>-3,7; 5,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,24</t>
+          <t>-3,96; 6,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,81</t>
+          <t>-4,64; 4,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 10,37</t>
+          <t>-0,3; 10,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,62</t>
+          <t>-1,41; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,71</t>
+          <t>-0,74; 5,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,16</t>
+          <t>-0,97; 6,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 213,39</t>
+          <t>-18,5; 186,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 237,52</t>
+          <t>-1,7; 238,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 120,81</t>
+          <t>-48,36; 119,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 99,23</t>
+          <t>-36,01; 104,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 78,4</t>
+          <t>-41,73; 70,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 150,79</t>
+          <t>-5,38; 171,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 96,87</t>
+          <t>-17,24; 93,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 96,11</t>
+          <t>-9,8; 103,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 103,0</t>
+          <t>-11,55; 111,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 9,12</t>
+          <t>-3,24; 9,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,57</t>
+          <t>-3,28; 7,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,06</t>
+          <t>-5,31; 5,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 5,04</t>
+          <t>-9,52; 4,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -2,78</t>
+          <t>-14,66; -2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,15; -2,61</t>
+          <t>-13,72; -2,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,05</t>
+          <t>-4,53; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,51</t>
+          <t>-7,03; 1,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,07</t>
+          <t>-7,81; 0,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 271,57</t>
+          <t>-42,92; 305,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 301,52</t>
+          <t>-34,24; 267,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 191,11</t>
+          <t>-58,34; 177,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 62,19</t>
+          <t>-60,53; 58,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,45; -27,28</t>
+          <t>-88,75; -26,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,22; -25,48</t>
+          <t>-83,95; -19,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 76,02</t>
+          <t>-38,16; 76,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 28,56</t>
+          <t>-59,23; 23,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,28; 3,02</t>
+          <t>-62,55; 6,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,65</t>
+          <t>-5,26; 5,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 2,52</t>
+          <t>-6,84; 3,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,96</t>
+          <t>-7,87; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 5,29</t>
+          <t>-3,43; 5,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,2</t>
+          <t>-2,93; 6,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,4</t>
+          <t>-0,92; 7,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,31</t>
+          <t>-3,24; 3,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,95</t>
+          <t>-3,48; 3,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,09</t>
+          <t>-2,52; 3,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 116,77</t>
+          <t>-54,43; 94,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 54,98</t>
+          <t>-68,09; 60,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 21,21</t>
+          <t>-72,65; 13,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 213,25</t>
+          <t>-54,99; 194,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 210,18</t>
+          <t>-50,34; 220,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 254,88</t>
+          <t>-14,94; 279,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 68,97</t>
+          <t>-44,1; 79,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 62,59</t>
+          <t>-46,69; 72,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 66,08</t>
+          <t>-32,56; 82,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,41</t>
+          <t>0,75; 6,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,66</t>
+          <t>-1,0; 4,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,77</t>
+          <t>-3,05; 2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,07</t>
+          <t>-1,63; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,15</t>
+          <t>-4,03; 1,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,01</t>
+          <t>-2,51; 2,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,26</t>
+          <t>0,36; 4,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,02</t>
+          <t>-1,62; 2,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,73</t>
+          <t>-1,89; 1,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 118,21</t>
+          <t>8,41; 121,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 85,52</t>
+          <t>-13,27; 86,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 33,79</t>
+          <t>-38,75; 40,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 58,71</t>
+          <t>-17,65; 61,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 18,43</t>
+          <t>-43,07; 18,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 44,99</t>
+          <t>-26,87; 42,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,12; 67,99</t>
+          <t>4,03; 71,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 33,18</t>
+          <t>-20,48; 31,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 26,33</t>
+          <t>-22,89; 25,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 16,61</t>
+          <t>2,46; 17,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 7,99</t>
+          <t>-4,94; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 9,48</t>
+          <t>-3,8; 9,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 10,52</t>
+          <t>-2,61; 11,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,14</t>
+          <t>-7,17; 5,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 6,54</t>
+          <t>-7,98; 6,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,59</t>
+          <t>1,54; 11,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,35</t>
+          <t>-4,23; 4,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,5</t>
+          <t>-4,04; 5,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 562,59</t>
+          <t>10,9; 498,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 265,8</t>
+          <t>-51,53; 255,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 304,34</t>
+          <t>-48,17; 319,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 249,64</t>
+          <t>-27,59; 240,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 126,75</t>
+          <t>-64,77; 126,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 148,92</t>
+          <t>-73,05; 165,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 267,17</t>
+          <t>15,13; 258,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 125,12</t>
+          <t>-43,93; 107,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 120,4</t>
+          <t>-46,21; 134,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 7,6</t>
+          <t>-1,29; 7,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 10,16</t>
+          <t>0,19; 9,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,03</t>
+          <t>-3,81; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 6,35</t>
+          <t>-3,85; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,55</t>
+          <t>-4,52; 4,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 10,63</t>
+          <t>-0,73; 10,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,6</t>
+          <t>-1,4; 5,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,74</t>
+          <t>-1,19; 5,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 6,49</t>
+          <t>-0,65; 6,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 186,14</t>
+          <t>-18,69; 177,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 238,29</t>
+          <t>-1,9; 235,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 119,74</t>
+          <t>-47,63; 118,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 104,41</t>
+          <t>-35,72; 92,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 70,22</t>
+          <t>-40,87; 68,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 171,58</t>
+          <t>-8,27; 161,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 93,15</t>
+          <t>-17,1; 95,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 103,06</t>
+          <t>-11,66; 98,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 111,89</t>
+          <t>-9,63; 113,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 9,23</t>
+          <t>-3,2; 9,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 7,99</t>
+          <t>-2,94; 8,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,57</t>
+          <t>-5,37; 5,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 4,44</t>
+          <t>-8,95; 4,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -2,89</t>
+          <t>-14,08; -2,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -2,17</t>
+          <t>-13,46; -2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 5,08</t>
+          <t>-4,32; 5,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,51</t>
+          <t>-7,09; 1,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 0,23</t>
+          <t>-7,83; 0,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 305,0</t>
+          <t>-41,44; 310,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 267,33</t>
+          <t>-34,74; 263,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 177,01</t>
+          <t>-52,08; 198,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 58,31</t>
+          <t>-57,63; 53,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,75; -26,12</t>
+          <t>-88,21; -26,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,95; -19,64</t>
+          <t>-83,79; -21,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 76,49</t>
+          <t>-39,49; 83,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 23,95</t>
+          <t>-59,61; 23,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 6,66</t>
+          <t>-65,4; 2,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,16</t>
+          <t>-5,81; 5,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,07</t>
+          <t>-7,17; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,61</t>
+          <t>-8,29; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,59</t>
+          <t>-3,06; 5,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,14</t>
+          <t>-2,7; 6,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 7,53</t>
+          <t>-0,38; 7,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,68</t>
+          <t>-2,89; 3,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,11</t>
+          <t>-3,53; 2,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,64</t>
+          <t>-2,99; 2,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 94,4</t>
+          <t>-60,24; 104,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 60,69</t>
+          <t>-70,56; 53,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,65; 13,84</t>
+          <t>-73,35; 17,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 194,08</t>
+          <t>-54,06; 209,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 220,11</t>
+          <t>-50,87; 236,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 279,52</t>
+          <t>-10,62; 279,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 79,59</t>
+          <t>-39,46; 87,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 72,52</t>
+          <t>-47,21; 62,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 82,41</t>
+          <t>-37,9; 60,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,63</t>
+          <t>0,79; 6,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,65</t>
+          <t>-0,64; 4,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,02</t>
+          <t>-3,15; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,02</t>
+          <t>-1,56; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,12</t>
+          <t>-4,03; 1,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,77</t>
+          <t>-2,49; 3,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,44</t>
+          <t>0,35; 4,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,07</t>
+          <t>-1,8; 1,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,61</t>
+          <t>-1,84; 1,72</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,41; 121,93</t>
+          <t>9,1; 128,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 86,89</t>
+          <t>-10,37; 95,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 40,44</t>
+          <t>-39,24; 30,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 61,61</t>
+          <t>-17,05; 56,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 18,13</t>
+          <t>-42,73; 18,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 42,87</t>
+          <t>-27,34; 46,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,03; 71,64</t>
+          <t>3,38; 67,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 31,94</t>
+          <t>-22,45; 28,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 25,69</t>
+          <t>-22,85; 27,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 17,0</t>
+          <t>-2,92; 11,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 7,6</t>
+          <t>-7,3; 5,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 9,55</t>
+          <t>-7,6; 6,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 11,1</t>
+          <t>2,12; 16,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 5,52</t>
+          <t>-4,99; 8,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 6,78</t>
+          <t>-3,67; 11,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,66</t>
+          <t>1,66; 11,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,85</t>
+          <t>-4,24; 4,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,88</t>
+          <t>-3,92; 6,04</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-9,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-14,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>152,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>30,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>38,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,66%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,72%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 498,51</t>
+          <t>-29,94; 223,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 255,72</t>
+          <t>-64,39; 129,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 319,95</t>
+          <t>-71,59; 158,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 240,73</t>
+          <t>9,94; 630,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 126,45</t>
+          <t>-49,41; 277,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 165,65</t>
+          <t>-44,58; 384,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 258,8</t>
+          <t>12,84; 236,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 107,2</t>
+          <t>-44,05; 103,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 134,55</t>
+          <t>-44,39; 124,54</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,09</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,89</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,48</t>
+          <t>-3,5; 6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,89</t>
+          <t>-4,37; 4,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,95</t>
+          <t>-1,65; 8,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,98</t>
+          <t>-1,02; 8,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 4,48</t>
+          <t>-0,23; 9,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 10,93</t>
+          <t>-3,55; 5,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,53</t>
+          <t>-1,05; 5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,72</t>
+          <t>-0,92; 5,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,65</t>
+          <t>-1,31; 5,44</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>51,93%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>82,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 177,33</t>
+          <t>-33,84; 99,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 235,73</t>
+          <t>-41,56; 78,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 118,18</t>
+          <t>-17,75; 129,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 92,4</t>
+          <t>-15,43; 213,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 68,3</t>
+          <t>-5,42; 237,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 161,92</t>
+          <t>-47,93; 119,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 95,31</t>
+          <t>-12,51; 96,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 98,24</t>
+          <t>-11,15; 96,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 113,92</t>
+          <t>-15,66; 91,53</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,99</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-7,3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,84</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,99</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,31</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 9,67</t>
+          <t>-9,03; 5,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,14</t>
+          <t>-14,35; -2,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 5,77</t>
+          <t>-14,14; -2,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,26</t>
+          <t>-3,74; 9,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -2,54</t>
+          <t>-3,03; 8,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -2,15</t>
+          <t>-4,56; 6,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,31</t>
+          <t>-4,49; 5,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,3</t>
+          <t>-7,19; 1,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,04</t>
+          <t>-7,79; 0,04</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-16,85%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-68,1%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-62,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>51,6%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>46,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-16,85%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-68,1%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-62,28%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-39,41%</t>
+          <t>-38,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 310,2</t>
+          <t>-61,03; 62,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 263,81</t>
+          <t>-88,45; -27,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 198,0</t>
+          <t>-85,5; -26,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 53,28</t>
+          <t>-42,97; 271,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,21; -26,27</t>
+          <t>-37,08; 301,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,79; -21,58</t>
+          <t>-51,17; 187,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 83,89</t>
+          <t>-40,35; 76,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 23,86</t>
+          <t>-60,29; 28,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,4; 2,01</t>
+          <t>-64,43; 3,12</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 5,37</t>
+          <t>-2,93; 5,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,81</t>
+          <t>-2,76; 6,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 0,8</t>
+          <t>-0,72; 7,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,4</t>
+          <t>-5,41; 5,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,48</t>
+          <t>-7,08; 2,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 7,58</t>
+          <t>-7,24; 1,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,9</t>
+          <t>-3,17; 3,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,89</t>
+          <t>-3,59; 2,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,97</t>
+          <t>-2,56; 3,51</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27,05%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>74,02%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-3,65%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-30,27%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-40,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>-34,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,24; 104,23</t>
+          <t>-49,29; 213,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 53,31</t>
+          <t>-49,44; 210,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 17,16</t>
+          <t>-15,67; 260,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 209,48</t>
+          <t>-55,81; 116,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 236,73</t>
+          <t>-67,23; 54,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 279,05</t>
+          <t>-67,25; 29,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 87,09</t>
+          <t>-40,41; 68,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 62,05</t>
+          <t>-48,02; 62,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 60,93</t>
+          <t>-31,56; 73,61</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,62</t>
+          <t>-1,78; 4,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,84</t>
+          <t>-3,93; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,68</t>
+          <t>-2,67; 2,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,88</t>
+          <t>0,45; 6,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,21</t>
+          <t>-0,95; 4,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,16</t>
+          <t>-2,6; 2,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,35</t>
+          <t>0,3; 4,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,88</t>
+          <t>-1,49; 2,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,72</t>
+          <t>-1,8; 1,76</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-17,02%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,51%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>54,91%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-8,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-3,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,1; 128,79</t>
+          <t>-20,85; 58,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 95,68</t>
+          <t>-41,85; 18,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 30,35</t>
+          <t>-29,43; 40,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 56,53</t>
+          <t>3,02; 118,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 18,61</t>
+          <t>-12,62; 85,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 46,24</t>
+          <t>-34,19; 42,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,38; 67,98</t>
+          <t>4,12; 67,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 28,57</t>
+          <t>-18,8; 33,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 27,28</t>
+          <t>-22,53; 28,33</t>
         </is>
       </c>
     </row>
